--- a/data/trans_dic/P17A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P17A-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,73; 35,57</t>
+          <t>29,96; 35,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 38,25</t>
+          <t>32,17; 38,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,02; 37,79</t>
+          <t>31,36; 38,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,78; 30,59</t>
+          <t>22,0; 28,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,68; 43,21</t>
+          <t>37,17; 42,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,08; 43,7</t>
+          <t>38,21; 43,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,99; 45,45</t>
+          <t>39,19; 45,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,91; 34,35</t>
+          <t>29,21; 33,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,75; 38,64</t>
+          <t>34,54; 38,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,74; 40,99</t>
+          <t>36,4; 40,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,68; 41,33</t>
+          <t>36,66; 41,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,57; 31,81</t>
+          <t>27,0; 30,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,07; 16,8</t>
+          <t>13,25; 16,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 20,27</t>
+          <t>16,6; 20,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,87; 24,55</t>
+          <t>20,57; 24,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 18,76</t>
+          <t>15,74; 19,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,37; 27,73</t>
+          <t>23,26; 27,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,96; 30,62</t>
+          <t>26,14; 30,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,84; 32,24</t>
+          <t>27,99; 32,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 29,22</t>
+          <t>20,9; 24,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,47</t>
+          <t>18,66; 21,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,74; 24,66</t>
+          <t>21,58; 24,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,8; 27,61</t>
+          <t>24,69; 27,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 23,48</t>
+          <t>18,91; 21,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,3; 16,4</t>
+          <t>10,14; 16,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 19,7</t>
+          <t>12,42; 20,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 26,06</t>
+          <t>18,66; 26,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 24,49</t>
+          <t>17,32; 24,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,73; 28,47</t>
+          <t>20,34; 28,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,7; 28,65</t>
+          <t>19,56; 28,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,76; 29,16</t>
+          <t>21,56; 29,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,49; 26,41</t>
+          <t>21,23; 26,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,0; 20,7</t>
+          <t>15,92; 20,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,96; 22,76</t>
+          <t>17,13; 22,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,0; 26,42</t>
+          <t>20,87; 26,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,02; 24,37</t>
+          <t>20,13; 24,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,43</t>
+          <t>18,79; 21,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,3; 24,31</t>
+          <t>21,47; 24,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 26,76</t>
+          <t>23,69; 26,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,65; 20,63</t>
+          <t>18,12; 20,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,29; 32,43</t>
+          <t>29,46; 32,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,92; 34,17</t>
+          <t>30,83; 34,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,16; 34,41</t>
+          <t>31,12; 34,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,73; 28,52</t>
+          <t>23,34; 25,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 26,78</t>
+          <t>24,59; 26,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,69; 28,97</t>
+          <t>26,76; 28,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,95; 30,14</t>
+          <t>27,98; 30,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,76; 23,97</t>
+          <t>21,34; 23,23</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>237602</t>
+          <t>257315</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>375114</t>
+          <t>404455</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>306489; 366613</t>
+          <t>308870; 367217</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>313421; 371970</t>
+          <t>312861; 377666</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>233968; 285099</t>
+          <t>236534; 288301</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122318; 157310</t>
+          <t>127123; 167091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>495495; 568286</t>
+          <t>488808; 561215</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>508675; 583692</t>
+          <t>510375; 586869</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>387781; 452103</t>
+          <t>389831; 453707</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>218047; 259019</t>
+          <t>239698; 278576</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>815310; 906525</t>
+          <t>810275; 905806</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>848149; 946236</t>
+          <t>840186; 943665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>641565; 722780</t>
+          <t>641236; 724709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>349752; 403465</t>
+          <t>377546; 433213</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369658</t>
+          <t>396232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>502340</t>
+          <t>489526</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>871998</t>
+          <t>885759</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>221157; 284212</t>
+          <t>224096; 284039</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>327532; 396431</t>
+          <t>324614; 397251</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>433324; 509700</t>
+          <t>427079; 507845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254846; 429608</t>
+          <t>350933; 432535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>370575; 439659</t>
+          <t>368878; 439789</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>454258; 535763</t>
+          <t>457336; 535157</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>553639; 641102</t>
+          <t>556598; 638516</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>376169; 653176</t>
+          <t>453120; 526106</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>611013; 703675</t>
+          <t>611594; 703777</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>805506; 913904</t>
+          <t>799661; 902088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1007968; 1122230</t>
+          <t>1003471; 1123007</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>721663; 1062593</t>
+          <t>831687; 938256</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133483</t>
+          <t>146384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>175952</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>286939</t>
+          <t>322337</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56787; 90433</t>
+          <t>55886; 89622</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58697; 94041</t>
+          <t>59297; 95479</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102147; 142523</t>
+          <t>102041; 144496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>113209; 158385</t>
+          <t>123279; 170929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>98749; 135621</t>
+          <t>96924; 135511</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90185; 131104</t>
+          <t>89540; 128219</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>119505; 160119</t>
+          <t>118395; 159243</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>135333; 174460</t>
+          <t>156007; 198166</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164422; 212774</t>
+          <t>163627; 214195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158603; 212814</t>
+          <t>160195; 213039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230155; 289554</t>
+          <t>228691; 289410</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>261742; 318500</t>
+          <t>291117; 357858</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640653</t>
+          <t>689757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>893399</t>
+          <t>922793</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1534051</t>
+          <t>1612550</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>610391; 701611</t>
+          <t>615137; 706471</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>725521; 827875</t>
+          <t>731106; 835169</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>803438; 903820</t>
+          <t>800128; 897496</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>505561; 711678</t>
+          <t>637711; 737746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>989297; 1095103</t>
+          <t>994968; 1102982</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1095530; 1210777</t>
+          <t>1092356; 1212825</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1100537; 1215254</t>
+          <t>1099194; 1213085</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>756728; 1040989</t>
+          <t>869286; 966749</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1642244; 1780854</t>
+          <t>1635480; 1776710</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1854722; 2012832</t>
+          <t>1859341; 2012915</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1931334; 2082648</t>
+          <t>1933405; 2083815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1332209; 1701723</t>
+          <t>1545917; 1682517</t>
         </is>
       </c>
     </row>
